--- a/output/market_cap_universe.xlsx
+++ b/output/market_cap_universe.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market_Cap_Universe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Market_Cap_Universe" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,23 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -61,21 +71,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -443,15 +450,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,6 +490,11 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>시총구분</t>
         </is>
       </c>
@@ -497,16 +510,21 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="3" t="n">
         <v>562365602590000</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>95000</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="E2" s="3" t="n">
+        <v>21050111</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -523,16 +541,21 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="3" t="n">
         <v>307580999212500</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>422500</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="E3" s="3" t="n">
+        <v>2688019</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -549,16 +572,21 @@
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>90441000000000</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>386500</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="n">
+        <v>320758</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -575,16 +603,21 @@
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>80213098000000</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>1127000</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="n">
+        <v>341106</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -593,24 +626,29 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>207940</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>80213098000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1127000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>60300527669600</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>73900</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3458114</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -619,24 +657,29 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>034020</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>KB금융</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>44135165317100</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>115700</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>53102519003400</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>82900</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>11930455</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -645,24 +688,29 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>000270</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>기아</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>40875326226000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>103800</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>49191484554000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>954000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>329226</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -671,24 +719,29 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>NAVER</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>40546406923000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>258500</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>45763360701000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>223500</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>670710</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -697,24 +750,29 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>329180</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>39536783164800</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>171200</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>45007969812000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>507000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>143062</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -723,24 +781,29 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>055550</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>신한지주</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>34518689807400</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>71100</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>44135165317100</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>115700</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1145113</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -749,24 +812,29 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>삼성생명</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>32440000000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>162200</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>40875326226000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>103800</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>598957</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -775,24 +843,29 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>035420</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>27584425747000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>300500</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>40546406923000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>258500</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1438737</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -801,24 +874,29 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>26185233769600</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>59200</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>39536783164800</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>171200</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>391762</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -827,24 +905,29 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>028260</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>한국전력</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>25261286429950</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>39350</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+          <t>삼성물산</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>35015168064000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>206000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>386262</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -853,24 +936,29 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>055550</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>24047350329600</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>86400</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>34518689807400</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>71100</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1062558</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -879,24 +967,29 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>LG화학</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>20754148842000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>294000</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+          <t>삼성생명</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>32440000000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>162200</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>355347</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -905,24 +998,29 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>삼성화재</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>20589991862500</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>447500</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>32273698923000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>243500</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>373309</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -931,24 +1029,29 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>042660</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>18755649976000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>25550</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+          <t>한화오션</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>32204047709400</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>105100</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1595415</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -957,24 +1060,29 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>18206985267600</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>107700</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
+          <t>HD한국조선해양</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>30255507090000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>427500</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>227271</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -983,24 +1091,29 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>012330</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>18206985267600</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>107700</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>27584425747000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>300500</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>162540</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1009,24 +1122,29 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>010130</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>17849694895000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>221500</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
+          <t>고려아연</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>26809762518000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1386000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>136729</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1035,24 +1153,29 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>16784375744500</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>231500</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>26185233769600</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>59200</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1659217</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1061,24 +1184,29 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>259960</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>크래프톤</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>13862594655000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>292500</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>25261286429950</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>39350</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>4292154</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1087,24 +1215,29 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>267260</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>13731322424100</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>84300</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
+          <t>HD현대일렉트릭</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>24079486180000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>668000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>211360</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1113,24 +1246,29 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>12775074780000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>165100</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
+          <t>하나금융지주</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>24047350329600</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>86400</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>609693</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1139,24 +1277,29 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>030200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>12437270154750</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>49350</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>23810075660000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>445000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>263546</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1165,24 +1308,29 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>247540</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>12244728268800</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>125200</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
+          <t>현대로템</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>23301879555500</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>213500</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>547346</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1191,24 +1339,29 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>11620141867300</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>54100</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
+          <t>POSCO홀딩스</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>22539827132000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>278500</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>247347</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1217,24 +1370,29 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>011200</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>하이브</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>11579282966000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>278000</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
+          <t>HMM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>20859553743600</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>20350</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1051718</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1243,24 +1401,29 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>003550</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>11196487071000</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>72600</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
+          <t>LG화학</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>20754148842000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>294000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>172127</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1269,24 +1432,29 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>323410</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>10756134354350</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>22550</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
+          <t>삼성화재</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>20589991862500</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>447500</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>48876</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1295,24 +1463,29 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>323410</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>10756134354350</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>22550</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
+          <t>메리츠금융지주</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>19870149058200</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>113400</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>226509</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1321,24 +1494,29 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>047050</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>8884100794000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>50500</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>18964000000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>21550</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>4269308</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1347,24 +1525,29 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>대한항공</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>8119265575050</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>22050</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>18755649976000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>25550</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1138563</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1373,24 +1556,29 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>한진칼</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>6502645974600</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>97400</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>18206985267600</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>107700</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>229656</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>5조이상</t>
         </is>
@@ -1399,180 +1587,6322 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>한미약품</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>4509468832000</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>352000</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>17849694895000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>221500</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>450096</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>1.5조이상</t>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>036570</t>
+          <t>034730</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>엔씨소프트</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>4448840543000</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>206500</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>16784375744500</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>231500</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>241248</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>1.5조이상</t>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>051900</t>
+          <t>033780</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>4315293438000</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>282000</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
+          <t>KT&amp;G</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>16362630648000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>136500</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>413797</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>1.5조이상</t>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>403870</t>
+          <t>003670</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>3022648161600</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>36200</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0</v>
+          <t>포스코퓨처엠</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>15494431524000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>174200</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>807770</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>1.5조이상</t>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>2996084355000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>82500</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
+          <t>효성중공업</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>15292258720000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1640000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>82647</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>1.5조이상</t>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>068760</t>
+          <t>024110</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>셀트리온제약</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>2349940529600</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>53800</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
+          <t>기업은행</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>15246782615280</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>19120</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>649252</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>1.5조이상</t>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>009150</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>14938739200000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>442942</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>259960</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>크래프톤</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>13862594655000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>292500</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>100373</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>066570</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>13731322424100</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>84300</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>788790</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>042700</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>13534332400000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>142000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>3313731</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>018260</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>삼성에스디에스</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>12775074780000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>165100</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>134191</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>030200</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>12437270154750</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>49350</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>467109</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>267250</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>HD현대</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>12394015036500</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>156900</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>301979</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>247540</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>에코프로비엠</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>12244728268800</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>125200</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>443808</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>006800</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>미래에셋증권</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>12233286951600</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>21450</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2097262</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>086280</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>현대글로비스</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>12202500000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>162700</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>125035</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>11620141867300</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>54100</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>598149</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>352820</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>하이브</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>11579282966000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>278000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>154640</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>003550</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>11196487071000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>72600</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>150645</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>323410</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>카카오뱅크</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>10756134354350</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>22550</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>689840</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>003230</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>삼양식품</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>10704414315000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1421000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>39591</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>443060</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>HD현대마린솔루션</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>10490035140000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>234000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>55429</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>272210</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>10088295372600</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>53400</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>930413</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>079550</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>LIG넥스원</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>10054000000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>457000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>99131</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>000150</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>두산</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>9897777165000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>599000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>121416</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>047810</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>한국항공우주</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>9747510700000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>407100</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>005830</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>DB손해보험</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>9458880000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>133600</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>252703</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>000100</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>9372300816400</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>117200</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>497849</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>278470</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>9282802440000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>248000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>251688</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>010120</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>LS ELECTRIC</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>9165000000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>305500</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>264311</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>047050</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>포스코인터내셔널</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>8884100794000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>50500</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>395507</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>071050</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>한국금융지주</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>8264164613600</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>148300</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>430612</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>003490</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>8119265575050</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>22050</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1184924</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>010620</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>HD현대미포</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>8008400874500</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>200500</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>191914</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>326030</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>SK바이오팜</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>7948794875000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>101500</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>117208</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>010950</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>7374172876000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>65500</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>221511</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>7245000000000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>14490</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>3010789</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>005940</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>NH투자증권</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>7037801287750</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>19750</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1135700</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>377300</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>카카오페이</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>6999343013600</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>51800</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>381616</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>086520</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>에코프로</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>6870273291200</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>50600</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>439055</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>000720</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>6848379547500</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>61500</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>2401538</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>090430</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>아모레퍼시픽</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>6837803527100</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>116900</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>174392</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>277810</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>6760850513000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>348500</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>239506</v>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>021240</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>코웨이</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>6730694848800</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>93600</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>409812</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>016360</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>삼성증권</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>6688570000000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>74900</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>363748</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>039490</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>키움증권</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>6649232940000</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>252000</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>147798</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>032640</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>LG유플러스</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>6520496145350</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>15170</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>1299406</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>180640</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>한진칼</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>6502645974600</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>97400</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>65199</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>000880</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>한화</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>6251558499000</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>83400</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>199046</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>087010</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>펩트론</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>6214073775000</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>266500</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>174741</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>064400</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>LG씨엔에스</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>6191012077200</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>63900</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>396748</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>005387</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>현대차2우B</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>5971839244000</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>170800</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>71990</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>006260</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>5861330000000</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>184900</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>235787</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>029780</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>삼성카드</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>5711843326300</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>49300</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>50598</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>007660</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>이수페타시스</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>5711237238200</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>77800</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>1629564</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>5703916752000</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>549000</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>129051</v>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>241560</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>두산밥캣</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>5559651770000</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>450291</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>5546800000000</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>28300</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>750234</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>088980</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>맥쿼리인프라</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>5478867599920</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>11440</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>1170845</v>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>141080</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>5275549705800</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>144100</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>344881</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>5067553935900</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>38550</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>394682</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>009830</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>4984883544000</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>29000</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>876291</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>161390</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>한국타이어앤테크놀로지</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>4979777773800</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>40200</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>310498</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>4966777366500</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>90100</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>443064</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>001040</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>4930912662000</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>169000</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>113097</v>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>251270</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>넷마블</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>4821991462200</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>56100</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>159127</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>000250</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>삼천당제약</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>4677419916800</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>199400</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>114615</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>454910</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>두산로보틱스</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>4660556562000</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>71900</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>658518</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>011070</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>LG이노텍</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>4643486393400</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>196200</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>280176</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>138930</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>BNK금융지주</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>4549731978380</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>14470</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>1060081</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>128940</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>4509468832000</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>352000</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>122063</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>036570</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>엔씨소프트</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>4448840543000</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>206500</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>81231</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>058470</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>4412666115000</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>57900</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>745341</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>004020</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>현대제철</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>4390366326500</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>32900</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>332714</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>175330</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>JB금융지주</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>4358975683200</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>22800</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>359632</v>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>051900</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>LG생활건강</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>4315293438000</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>282000</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>32743</v>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>078930</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>4209066623400</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>45300</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>185431</v>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>307950</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>현대오토에버</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>4124566892800</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>150400</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>45541</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>011790</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>SKC</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>4032973737000</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>106500</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>177325</v>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>271560</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>오리온</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>3997102945200</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>101100</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>111188</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>005385</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>현대차우</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>3963295008000</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>169800</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>82278</v>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>082740</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>한화엔진</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>3942877459500</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>47250</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>2431836</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>035250</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>강원랜드</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>3773910420000</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>17640</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>296011</v>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>036460</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>한국가스공사</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>3729445200000</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>40400</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>496289</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>103140</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>풍산</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>3704809551600</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>132200</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>329219</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>052690</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>3695874000000</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>96700</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>1176157</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>062040</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>산일전기</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>3686913720000</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>121100</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>1132434</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>950160</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>코오롱티슈진</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>3686702039500</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>44300</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>148343</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>302440</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>SK바이오사이언스</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>3620654499000</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>46200</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>63077</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>031210</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>서울보증보험</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>3539955018600</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>50700</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>48358</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>450080</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>에코프로머티</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>3517600927200</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>50300</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>189962</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>097950</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>CJ제일제당</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>3507625338000</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>233000</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>66706</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>002380</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>KCC</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>3443507512500</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>387500</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>33434</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>214370</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>케어젠</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>3357187500000</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>62500</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>62098</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>145020</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>3352848992500</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>272500</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>146761</v>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>022100</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>포스코DX</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>3337162301550</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>21950</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>231738</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>3260963277000</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>17490</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>2279993</v>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>017800</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>현대엘리베이터</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>3229031001000</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>82600</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>421692</v>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>039030</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>3159964575000</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>256500</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>109941</v>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>071970</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>HD현대마린엔진</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>3134346138000</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>92400</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>508808</v>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>214150</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>클래시스</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>3065664841200</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>46800</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>642993</v>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>403870</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>3022648161600</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>36200</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>720293</v>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>066970</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>엘앤에프</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>2996084355000</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>82500</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>486681</v>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>004990</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>롯데지주</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>2989913254500</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>164272</v>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>310210</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>2973892775700</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>161700</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>104785</v>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>439260</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>대한조선</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>2966526024000</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>77000</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>193501</v>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>011170</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>롯데케미칼</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>2934393743400</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>68600</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>128384</v>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>012750</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>에스원</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>2906937117000</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>76500</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>199625</v>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>011780</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>금호석유화학</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>2897324776500</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>109500</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>80883</v>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>042670</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>HD현대인프라코어</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>2862984768080</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>15160</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>1238746</v>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>041510</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>에스엠</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>2772546959000</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>121100</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>151703</v>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>088350</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>2761925400000</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>3180</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>780385</v>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>012510</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>더존비즈온</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>2761795065600</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>90900</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>110270</v>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>111770</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>영원무역</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>2711861841600</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>61200</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>40385</v>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>2684889384700</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>54700</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>731357</v>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>108490</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>2677163400000</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>202500</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>2337088</v>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>489790</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>한화비전</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>2670835831000</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>52900</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>417792</v>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>026960</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>동서</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>2657005000000</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>26650</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>76520</v>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>2651802211800</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>43350</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>415200</v>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>004370</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>농심</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>2630742665000</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>432500</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>31321</v>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>000990</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>DB하이텍</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>2610636974400</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>58800</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>536515</v>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>035900</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>JYP Ent.</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>2597425165200</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>73100</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>432114</v>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>008930</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>한미사이언스</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>2513389462500</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>36750</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>81620</v>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>001450</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>2476380000000</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>27700</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>532342</v>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>383220</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>F&amp;F</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>2466975630000</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>64400</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>70299</v>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>361610</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>SK아이이테크놀로지</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>2429076870000</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>29700</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>146295</v>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>014680</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>한솔케미칼</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>2420064132500</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>213500</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>90220</v>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>068760</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>셀트리온제약</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>2349940529600</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>53800</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>78714</v>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>030000</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>제일기획</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>2323832745000</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>20200</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>630248</v>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>192820</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>코스맥스</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>2303950327000</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>203000</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>59653</v>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>동진쎄미켐</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>2298227881800</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>44700</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>360839</v>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>089030</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>테크윙</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>2297249167500</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>61500</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>738308</v>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>263750</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>펄어비스</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>2296860816250</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>35750</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>96528</v>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>081660</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>미스토홀딩스</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>2274627506150</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>37850</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>75625</v>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>357780</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>솔브레인</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>2244116291000</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>288500</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>45778</v>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>462870</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>시프트업</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>2239583532000</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>38100</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>54996</v>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>051600</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>한전KPS</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>2238750000000</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>49750</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>315578</v>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>139130</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>iM금융지주</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>2229872204160</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>13760</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>1289928</v>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>018670</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>SK가스</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>2218858560000</v>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>3815</v>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>001720</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>신영증권</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>2209536000000</v>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>134400</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>12370</v>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>003570</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>SNT다이내믹스</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>2184702192900</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>65700</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>41765</v>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>336260</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>2174391703200</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>33200</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>1407506</v>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>000240</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>한국앤컴퍼니</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>2150283186000</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>22650</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>60036</v>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>018880</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>한온시스템</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>2141495851560</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>3155</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>692138</v>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>140410</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>메지온</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>2140204699600</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>70900</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>114888</v>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>160190</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>하이젠알앤엠</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>2131272000000</v>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>69000</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>2900825</v>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>003690</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>코리안리</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>2123549237900</v>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>10900</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>612443</v>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>064760</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>2107337500000</v>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>180500</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>83844</v>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>002790</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>아모레퍼시픽홀딩스</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>2050021044000</v>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>25800</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>123674</v>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>139480</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>이마트</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>2047609769800</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>74200</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>137600</v>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>097230</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>HJ중공업</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>2015237600200</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>3079107</v>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>017960</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>한국카본</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>1995879979400</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>38450</v>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>1136599</v>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>028670</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>1975234346840</v>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>3695</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>2499188</v>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>1974521466000</v>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>95400</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>145323</v>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>103590</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>일진전기</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>1967022337500</v>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>41250</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>1248680</v>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>008770</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>호텔신라</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>1954556425800</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>49800</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>265342</v>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>226950</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>1931019168000</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>96000</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>971415</v>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>023530</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>롯데쇼핑</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>1895346585000</v>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>67000</v>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>146918</v>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>082270</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>젬백스</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>1894850567100</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>44700</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>204148</v>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>006040</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>동원산업</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>1893948599400</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>42900</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>163531</v>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>000120</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>CJ대한통운</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>1879737145600</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>82400</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>57034</v>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>483650</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>달바글로벌</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>1871715080000</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>152000</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>69723</v>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>347850</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>1871629395600</v>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>172400</v>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>335913</v>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>020560</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>아시아나항공</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>1864215934550</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>9050</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>82835</v>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>112610</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>씨에스윈드</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>1842890311100</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>43700</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>115745</v>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>069960</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>현대백화점</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>1828408090400</v>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>80800</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>116796</v>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>282330</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>BGF리테일</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>1823452083000</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>105500</v>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>42635</v>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>084370</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>유진테크</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>1817242130600</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>79300</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>192844</v>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>009970</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>영원무역홀딩스</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>1811597605400</v>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>134200</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>8535</v>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>009420</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>1807526074800</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>34600</v>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>249255</v>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>010060</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>OCI홀딩스</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>1804350540300</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>95900</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>216849</v>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>122870</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>와이지엔터테인먼트</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>1790602494200</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>95800</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>432344</v>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
           <t>161890</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B209" s="3" t="inlineStr">
         <is>
           <t>한국콜마</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C209" s="3" t="n">
         <v>1786904328900</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D209" s="3" t="n">
         <v>75700</v>
       </c>
-      <c r="E43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="E209" s="3" t="n">
+        <v>87835</v>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>034230</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>파라다이스</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>1775110788390</v>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>19210</v>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>1320878</v>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>484870</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>엠앤씨솔루션</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>1756633410000</v>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>191900</v>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>13991</v>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>067310</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>1756206648500</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>26500</v>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>1512854</v>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>1734857059600</v>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>51100</v>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>759352</v>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>140860</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="n">
+        <v>1731355807500</v>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>247500</v>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v>37822</v>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>095340</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>1708482874800</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>80600</v>
+      </c>
+      <c r="E215" s="3" t="n">
+        <v>131254</v>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>030530</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>원익홀딩스</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>1706959380100</v>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>22100</v>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>3749483</v>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>083650</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>비에이치아이</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>1692657312500</v>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>54700</v>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v>1866017</v>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>004170</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>신세계</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>1683084084500</v>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>174500</v>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v>35228</v>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>004800</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>효성</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>1679062822100</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>100300</v>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v>112390</v>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>267270</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>HD현대건설기계</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>1654180518900</v>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>95300</v>
+      </c>
+      <c r="E220" s="3" t="n">
+        <v>129712</v>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>006360</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>1650866942100</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>19290</v>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>560649</v>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>348370</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>엔켐</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>1630381630500</v>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>74900</v>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>137645</v>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>375500</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>DL이앤씨</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>1625132166000</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>201619</v>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>353200</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>대덕전자</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>1623345986250</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>32850</v>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>1521382</v>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>005850</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>에스엘</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>1618730922000</v>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>34850</v>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>90458</v>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>204270</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>제이앤티씨</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>1599510084900</v>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>27650</v>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>1324250</v>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>039200</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>1591415321600</v>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E227" s="3" t="n">
+        <v>350026</v>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>007310</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>오뚜기</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>1575077190000</v>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>393000</v>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>4615</v>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>000155</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>두산우</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>1564614873000</v>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>391500</v>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>32328</v>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>069620</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>1563028967500</v>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>134900</v>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>34117</v>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>204320</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>HL만도</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>1554280672000</v>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>33100</v>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>104070</v>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="n">
+        <v>1550272439740</v>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>1934751</v>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>457190</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>이수스페셜티케미컬</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>1549684764000</v>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>51300</v>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>283820</v>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>023590</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>다우기술</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>1543411624800</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>34400</v>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>47173</v>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>1527633797150</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>38050</v>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>558447</v>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>006280</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>녹십자</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>1526261862800</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>130600</v>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>31910</v>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>317450</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>명인제약</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>1521320000000</v>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>104200</v>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>730794</v>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>005070</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>코스모신소재</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>1519877843000</v>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>46750</v>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>954076</v>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>065350</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>신성델타테크</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>1511617140000</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>503973</v>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>1.5조이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>036930</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>1503132607800</v>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>31800</v>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>406222</v>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
         <is>
           <t>1.5조이상</t>
         </is>
